--- a/site/ab_leads.xlsx
+++ b/site/ab_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,29 +570,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Onoway</t>
+          <t>Coppermine Creek</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>METID_0315</t>
+          <t>METID_0022</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Producer - byproduct</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -625,12 +625,284 @@
         <v>35</v>
       </c>
       <c r="V2" t="n">
+        <v>49.1087</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-113.96088</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Villeneuve</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>METID_0317</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Producer - byproduct</t>
+        </is>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" t="n">
+        <v>325</v>
+      </c>
+      <c r="U3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V3" t="n">
+        <v>53.6781</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-113.80978</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Onoway</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>METID_0315</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Producer - byproduct</t>
+        </is>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T4" t="n">
+        <v>325</v>
+      </c>
+      <c r="U4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" t="n">
         <v>53.63997</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W4" t="n">
         <v>-114.14357</v>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Coppermine Creek</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>METID_0021</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="n">
+        <v>325</v>
+      </c>
+      <c r="U5" t="n">
+        <v>29</v>
+      </c>
+      <c r="V5" t="n">
+        <v>49.10869</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-113.96088</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Oldman River</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>METID_0231</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lead, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" t="n">
+        <v>325</v>
+      </c>
+      <c r="U6" t="n">
+        <v>29</v>
+      </c>
+      <c r="V6" t="n">
+        <v>50.12804</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-114.72253</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/site/ab_leads.xlsx
+++ b/site/ab_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,29 +570,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Coppermine Creek</t>
+          <t>Onoway</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>METID_0022</t>
+          <t>METID_0315</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Producer - byproduct</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -625,284 +625,12 @@
         <v>35</v>
       </c>
       <c r="V2" t="n">
-        <v>49.1087</v>
+        <v>53.63997</v>
       </c>
       <c r="W2" t="n">
-        <v>-113.96088</v>
+        <v>-114.14357</v>
       </c>
       <c r="X2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Villeneuve</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>METID_0317</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Producer - byproduct</t>
-        </is>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>13</v>
-      </c>
-      <c r="T3" t="n">
-        <v>325</v>
-      </c>
-      <c r="U3" t="n">
-        <v>35</v>
-      </c>
-      <c r="V3" t="n">
-        <v>53.6781</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-113.80978</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Onoway</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>METID_0315</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Producer - byproduct</t>
-        </is>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>13</v>
-      </c>
-      <c r="T4" t="n">
-        <v>325</v>
-      </c>
-      <c r="U4" t="n">
-        <v>35</v>
-      </c>
-      <c r="V4" t="n">
-        <v>53.63997</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-114.14357</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Coppermine Creek</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>METID_0021</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T5" t="n">
-        <v>325</v>
-      </c>
-      <c r="U5" t="n">
-        <v>29</v>
-      </c>
-      <c r="V5" t="n">
-        <v>49.10869</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-113.96088</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Oldman River</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>METID_0231</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lead, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>13</v>
-      </c>
-      <c r="T6" t="n">
-        <v>325</v>
-      </c>
-      <c r="U6" t="n">
-        <v>29</v>
-      </c>
-      <c r="V6" t="n">
-        <v>50.12804</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-114.72253</v>
-      </c>
-      <c r="X6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/site/ab_leads.xlsx
+++ b/site/ab_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,29 +570,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Onoway</t>
+          <t>Coppermine Creek</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>METID_0315</t>
+          <t>METID_0022</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Producer - byproduct</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -625,12 +625,148 @@
         <v>35</v>
       </c>
       <c r="V2" t="n">
-        <v>53.63997</v>
+        <v>49.1087</v>
       </c>
       <c r="W2" t="n">
-        <v>-114.14357</v>
+        <v>-113.96088</v>
       </c>
       <c r="X2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Coppermine Creek</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>METID_0021</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" t="n">
+        <v>325</v>
+      </c>
+      <c r="U3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V3" t="n">
+        <v>49.10869</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-113.96088</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Oldman River</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>METID_0231</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lead, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T4" t="n">
+        <v>325</v>
+      </c>
+      <c r="U4" t="n">
+        <v>29</v>
+      </c>
+      <c r="V4" t="n">
+        <v>50.12804</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-114.72253</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
